--- a/data/export/2026-09-27-operations.xlsx
+++ b/data/export/2026-09-27-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -991,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1024,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1048,33 +1076,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1179,7 +1211,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1190,7 +1222,7 @@
       <c r="AC6" s="2" t="inlineStr"/>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1983,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2103,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2527,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2537,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2630,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2807,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2923,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2978,3179 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>65分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>75分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>72分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-operations.xlsx
+++ b/data/export/2026-09-27-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD48"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1025,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:44</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1139,32 +1139,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1196,17 +1200,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1216,13 +1220,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1922,7 +1970,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2075,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2108,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2162,7 +2210,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2436,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,7 +2561,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2521,28 +2573,28 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2691,12 +2747,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2807,12 +2867,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3039,12 +3107,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3151,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3155,12 +3227,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3246,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3271,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3347,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3366,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3391,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -3339,60 +3419,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3416,33 +3500,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3455,60 +3543,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3624,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3667,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3581,7 +3677,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3591,40 +3687,44 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,17 +3748,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3668,13 +3768,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3697,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3707,40 +3811,44 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3862,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3764,33 +3872,37 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3803,22 +3915,22 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3851,12 +3963,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3982,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3906,7 +4018,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3919,7 +4031,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3929,7 +4041,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3967,12 +4079,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4134,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4147,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4045,7 +4157,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4055,40 +4167,44 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4218,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4112,17 +4228,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4132,13 +4248,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4271,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4161,7 +4281,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4199,12 +4319,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4338,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4374,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4387,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4277,7 +4397,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4315,12 +4435,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4490,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4383,22 +4503,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4431,12 +4551,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4570,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4606,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4499,22 +4619,22 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4552,7 +4672,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4686,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,7 +4722,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4735,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4625,7 +4745,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4663,12 +4783,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4802,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4718,7 +4838,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4851,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4741,7 +4861,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4779,12 +4899,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4918,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4834,77 +4954,73 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4918,7 +5034,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4928,107 +5044,99 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5042,7 +5150,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5052,107 +5160,99 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5166,7 +5266,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5176,17 +5276,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5196,87 +5296,79 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>72.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5290,7 +5382,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5300,17 +5392,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5320,45 +5412,41 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5391,12 +5479,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5410,7 +5498,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5446,35 +5534,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5507,12 +5595,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5526,7 +5614,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5562,35 +5650,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5623,12 +5711,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5642,7 +5730,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5678,35 +5766,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5739,12 +5827,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5758,7 +5846,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5783,50 +5871,46 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5859,12 +5943,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5878,7 +5962,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5914,35 +5998,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5975,12 +6059,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5994,7 +6078,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6030,35 +6114,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6091,12 +6175,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6110,47 +6194,3027 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>65分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>73分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:43</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="W48" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X48" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y48" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z48" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB48" s="2" t="inlineStr">
+      <c r="AB66" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AD48" s="2" t="inlineStr">
-        <is>
-          <t>3/9</t>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>6/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-operations.xlsx
+++ b/data/export/2026-09-27-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,17 +1215,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,7 +1964,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,12 +2088,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2123,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2180,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2243,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2276,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -2359,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2392,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2416,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2479,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2512,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2536,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2599,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2632,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2656,32 +2688,32 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
@@ -2752,7 +2784,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2839,32 +2871,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2872,7 +2908,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2896,37 +2932,37 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2992,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3031,7 +3067,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3046,7 +3082,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3148,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3151,7 +3187,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3166,7 +3202,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3268,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3276,12 +3312,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
@@ -3299,22 +3335,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3347,12 +3383,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3366,7 +3402,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3391,7 +3427,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3401,82 +3437,78 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3522,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3500,107 +3532,103 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3642,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,107 +3652,103 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3762,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3748,107 +3772,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3862,7 +3882,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3872,65 +3892,65 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3963,12 +3983,12 @@
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3982,7 +4002,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4007,46 +4027,50 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -4079,12 +4103,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4098,7 +4122,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4123,88 +4147,88 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4218,7 +4242,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4228,37 +4252,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4271,60 +4295,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4338,7 +4366,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4348,33 +4376,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -4387,60 +4419,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4454,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4464,33 +4500,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4543,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4513,7 +4553,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4523,40 +4563,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4570,7 +4614,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4580,33 +4624,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4667,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4629,7 +4677,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4639,40 +4687,44 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4686,7 +4738,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4696,33 +4748,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -4735,60 +4791,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4802,7 +4862,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4812,33 +4872,37 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4915,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4861,7 +4925,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4899,12 +4963,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4918,7 +4982,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4943,7 +5007,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4954,7 +5018,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4967,7 +5031,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4977,7 +5041,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4987,40 +5051,44 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5034,7 +5102,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5044,33 +5112,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5155,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5093,7 +5165,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5103,40 +5175,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5150,7 +5226,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5160,33 +5236,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5279,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5209,7 +5289,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5219,40 +5299,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5266,7 +5350,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5276,17 +5360,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5296,13 +5380,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5315,60 +5403,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5382,7 +5474,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5392,33 +5484,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5431,52 +5527,56 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -5484,7 +5584,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5498,7 +5598,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5508,33 +5608,37 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5651,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5557,7 +5661,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5567,12 +5671,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq37推进至seq59，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5595,12 +5699,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5608,13 +5712,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置浦建路锦绣路 ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5650,7 +5770,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5663,22 +5783,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5711,12 +5831,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5730,7 +5850,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5766,7 +5886,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5779,60 +5899,64 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5846,7 +5970,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5856,33 +5980,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5895,32 +6023,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq42推进至seq53，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5943,12 +6071,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5956,13 +6084,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5998,7 +6138,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6011,22 +6151,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6059,12 +6199,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6078,7 +6218,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6114,7 +6254,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6267,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6137,7 +6277,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6175,12 +6315,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6194,7 +6334,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6230,7 +6370,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6383,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6253,7 +6393,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6291,12 +6431,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6310,7 +6450,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6346,7 +6486,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6499,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6369,7 +6509,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6407,12 +6547,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6426,7 +6566,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6462,7 +6602,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6475,22 +6615,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6523,12 +6663,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6542,7 +6682,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6578,7 +6718,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6591,22 +6731,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6639,12 +6779,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6658,7 +6798,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6683,22 +6823,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>129.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6847,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6721,7 +6857,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6759,12 +6895,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6778,7 +6914,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6803,22 +6939,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6831,7 +6963,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6841,7 +6973,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6879,12 +7011,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6898,7 +7030,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6934,7 +7066,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6947,22 +7079,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6995,12 +7127,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7014,7 +7146,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7039,92 +7171,84 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>65分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7138,7 +7262,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7148,107 +7272,99 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7262,7 +7378,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7272,107 +7388,99 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7386,7 +7494,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7396,107 +7504,99 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7510,7 +7610,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7520,17 +7620,17 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7545,82 +7645,78 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7634,7 +7730,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7644,17 +7740,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7669,82 +7765,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7758,7 +7850,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7768,65 +7860,61 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7859,12 +7947,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7878,7 +7966,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7903,46 +7991,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7975,12 +8067,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7994,7 +8086,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8029,40 +8121,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8095,12 +8187,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8114,7 +8206,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8139,46 +8231,50 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8211,12 +8307,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8230,7 +8326,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8255,46 +8351,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8327,12 +8427,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8346,7 +8446,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8376,45 +8476,41 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8447,12 +8543,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8466,7 +8562,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8501,40 +8597,40 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8567,12 +8663,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8586,7 +8682,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8611,50 +8707,46 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8687,12 +8779,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8706,7 +8798,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8731,46 +8823,50 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -8803,12 +8899,12 @@
       <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8822,7 +8918,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8857,40 +8953,40 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8923,12 +9019,12 @@
       <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8942,7 +9038,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8967,18 +9063,22 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8991,60 +9091,64 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>65分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9058,7 +9162,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9068,33 +9172,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9107,60 +9215,64 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9174,47 +9286,2935 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>83分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>81分钟</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X88" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AB89" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>83.0</t>
-        </is>
-      </c>
-      <c r="AD73" s="2" t="inlineStr">
-        <is>
-          <t>5/12</t>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-27-operations.xlsx
+++ b/data/export/2026-09-27-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5808,17 +5808,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6672,17 +6672,17 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7912,17 +7912,17 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -9837,12 +9837,12 @@
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9939,32 +9939,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9972,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,17 +10000,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10016,17 +10020,17 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -10059,32 +10063,36 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10092,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10116,17 +10124,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -10136,7 +10144,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -10212,7 +10220,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10332,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10386,7 +10394,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10460,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10496,17 +10504,17 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -10630,7 +10638,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10832,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -11192,7 +11200,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11246,7 +11254,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11378,7 @@
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11494,7 +11502,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11696,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11742,7 +11750,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11856,17 +11864,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12192,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12246,7 +12254,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12444,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12568,7 +12576,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12612,17 +12620,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12824,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12940,7 +12948,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13064,7 +13072,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13113,12 +13121,12 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13196,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13237,12 +13245,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13436,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13606,7 +13614,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13676,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13725,12 +13733,12 @@
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14180,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14296,7 +14304,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14722,7 +14730,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14800,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14846,7 +14854,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -14970,7 +14978,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -15168,7 +15176,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15212,17 +15220,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15292,7 +15300,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15346,7 +15354,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15416,7 +15424,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15470,7 +15478,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15672,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15708,17 +15716,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15788,7 +15796,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15912,7 +15920,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16160,7 +16168,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16284,7 +16292,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16333,12 +16341,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16416,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16457,12 +16465,12 @@
       </c>
       <c r="AC129" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -16532,7 +16540,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -16834,7 +16842,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17036,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17206,7 +17214,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17788,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -18028,7 +18036,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18072,17 +18080,17 @@
       </c>
       <c r="AB142" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -18152,7 +18160,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18276,7 +18284,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18325,12 +18333,12 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18462,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18710,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19082,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19198,7 +19206,7 @@
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -19524,7 +19532,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19568,17 +19576,17 @@
       </c>
       <c r="AB154" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19648,7 +19656,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19697,12 +19705,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19776,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19822,7 +19830,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19900,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -20016,7 +20024,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20140,7 +20148,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20260,7 +20268,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20384,7 +20392,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20438,7 +20446,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -20508,7 +20516,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20562,7 +20570,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -20632,7 +20640,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -20810,7 +20818,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -21000,7 +21008,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21546,7 +21554,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -21841,24 +21849,24 @@
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
@@ -21868,7 +21876,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21917,12 +21925,12 @@
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -21965,24 +21973,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21992,7 +22000,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22041,12 +22049,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>127.2</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -22079,32 +22087,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -22112,7 +22124,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22136,17 +22148,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22156,17 +22168,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.8</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -22209,12 +22221,12 @@
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr"/>
@@ -22236,7 +22248,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22285,12 +22297,12 @@
       </c>
       <c r="AC176" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22323,32 +22335,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:04</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -22356,7 +22372,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22380,17 +22396,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22400,17 +22416,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22448,7 +22464,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22476,7 +22492,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22612,7 +22628,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22732,7 +22748,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22786,7 +22802,7 @@
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -22852,7 +22868,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22939,12 +22955,12 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -22972,18 +22988,34 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R182" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="Q182" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="R182" s="2" t="inlineStr"/>
-      <c r="S182" s="2" t="inlineStr"/>
-      <c r="T182" s="2" t="inlineStr"/>
-      <c r="U182" s="2" t="inlineStr"/>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="U182" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V182" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -23092,7 +23124,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23146,7 +23178,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -23212,7 +23244,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23332,7 +23364,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23452,7 +23484,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23506,7 +23538,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -23572,7 +23604,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23692,7 +23724,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23741,12 +23773,12 @@
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -24436,7 +24468,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24480,12 +24512,12 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24610,7 +24642,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -24928,7 +24960,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24972,17 +25004,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -25420,7 +25452,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25464,7 +25496,7 @@
       </c>
       <c r="AB202" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC202" s="2" t="inlineStr">
@@ -25792,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25846,7 +25878,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25916,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25960,12 +25992,12 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
@@ -26040,7 +26072,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26084,12 +26116,12 @@
       </c>
       <c r="AB207" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26342,7 +26374,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26784,7 +26816,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26828,17 +26860,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27280,7 +27312,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27324,7 +27356,7 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
@@ -27404,7 +27436,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27448,12 +27480,12 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
@@ -27528,7 +27560,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27582,7 +27614,7 @@
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27896,7 +27928,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27940,12 +27972,12 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
@@ -28020,7 +28052,7 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q223" s="2" t="inlineStr">
@@ -28064,17 +28096,17 @@
       </c>
       <c r="AB223" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC223" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -28198,7 +28230,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -28392,7 +28424,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28436,7 +28468,7 @@
       </c>
       <c r="AB226" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC226" s="2" t="inlineStr">
@@ -28640,7 +28672,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28694,7 +28726,7 @@
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28888,7 +28920,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28932,12 +28964,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -29190,7 +29222,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -29260,7 +29292,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -30128,7 +30160,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30172,17 +30204,17 @@
       </c>
       <c r="AB240" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -30252,7 +30284,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30430,7 +30462,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -30748,7 +30780,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30792,7 +30824,7 @@
       </c>
       <c r="AB245" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC245" s="2" t="inlineStr">
@@ -30996,7 +31028,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31050,7 +31082,7 @@
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -31364,7 +31396,7 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q250" s="2" t="inlineStr">
@@ -31408,12 +31440,12 @@
       </c>
       <c r="AB250" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC250" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD250" s="2" t="inlineStr">
@@ -31488,7 +31520,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31532,17 +31564,17 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31732,7 +31764,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31776,12 +31808,12 @@
       </c>
       <c r="AB253" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
@@ -31910,7 +31942,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31980,7 +32012,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32468,7 +32500,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32512,7 +32544,7 @@
       </c>
       <c r="AB259" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC259" s="2" t="inlineStr">
@@ -32712,7 +32744,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32766,7 +32798,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -33208,7 +33240,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33252,12 +33284,12 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33456,7 +33488,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33500,12 +33532,12 @@
       </c>
       <c r="AB267" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33576,7 +33608,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33620,17 +33652,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33700,7 +33732,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33878,7 +33910,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -34312,7 +34344,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34356,7 +34388,7 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
@@ -34560,7 +34592,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34614,7 +34646,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -35143,32 +35175,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -35176,7 +35212,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35200,17 +35236,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35220,12 +35256,12 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35383,32 +35419,36 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr"/>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N283" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O283" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -35416,7 +35456,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35440,17 +35480,17 @@
       </c>
       <c r="X283" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y283" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z283" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA283" s="2" t="inlineStr">
@@ -35460,17 +35500,17 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35623,32 +35663,36 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O285" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35656,7 +35700,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35680,17 +35724,17 @@
       </c>
       <c r="X285" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y285" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z285" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA285" s="2" t="inlineStr">
@@ -35700,12 +35744,12 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35776,7 +35820,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35863,32 +35907,36 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N287" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O287" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -35896,7 +35944,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35920,17 +35968,17 @@
       </c>
       <c r="X287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y287" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z287" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA287" s="2" t="inlineStr">
@@ -35940,7 +35988,7 @@
       </c>
       <c r="AB287" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC287" s="2" t="inlineStr">
@@ -36016,7 +36064,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36070,7 +36118,7 @@
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -36136,7 +36184,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36180,12 +36228,12 @@
       </c>
       <c r="AB289" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36256,7 +36304,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">

--- a/data/export/2026-09-27-operations.xlsx
+++ b/data/export/2026-09-27-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7292,12 +7292,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9728,7 +9728,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10149,7 +10149,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10187,32 +10187,36 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10220,7 +10224,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10244,17 +10248,17 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -10264,12 +10268,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10340,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10460,7 +10464,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10832,7 +10836,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10876,17 +10880,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11204,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11254,7 +11258,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11820,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11869,7 +11873,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -12200,7 +12204,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12244,17 +12248,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12386,7 +12390,7 @@
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12452,7 +12456,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12824,7 +12828,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12878,7 +12882,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12952,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -13072,7 +13076,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13126,7 +13130,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -13436,7 +13440,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -14180,7 +14184,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14304,7 +14308,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14348,17 +14352,17 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14854,7 +14858,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15176,7 +15180,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15225,7 +15229,7 @@
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
@@ -15300,7 +15304,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15424,7 +15428,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15468,17 +15472,17 @@
       </c>
       <c r="AB121" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC121" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -15796,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15920,7 +15924,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15974,7 +15978,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16172,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16292,7 +16296,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16346,7 +16350,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -16540,7 +16544,7 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q130" s="2" t="inlineStr">
@@ -17036,7 +17040,7 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q134" s="2" t="inlineStr">
@@ -17842,7 +17846,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18164,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -19532,7 +19536,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19581,7 +19585,7 @@
       </c>
       <c r="AC154" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD154" s="2" t="inlineStr">
@@ -19776,7 +19780,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19820,17 +19824,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -19954,7 +19958,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -20024,7 +20028,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20078,7 +20082,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -20148,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20192,17 +20196,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -20268,7 +20272,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20392,7 +20396,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20446,7 +20450,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -20516,7 +20520,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20640,7 +20644,7 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q163" s="2" t="inlineStr">
@@ -21008,7 +21012,7 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q166" s="2" t="inlineStr">
@@ -21876,7 +21880,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21930,7 +21934,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -22345,24 +22349,24 @@
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>21:04</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N177" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O177" s="2" t="inlineStr">
@@ -22372,7 +22376,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22421,7 +22425,7 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
@@ -22464,7 +22468,7 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
+          <t>原方向在全程49%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
@@ -22492,7 +22496,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22595,32 +22599,36 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22628,7 +22636,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22652,17 +22660,17 @@
       </c>
       <c r="X179" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z179" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA179" s="2" t="inlineStr">
@@ -22672,17 +22680,17 @@
       </c>
       <c r="AB179" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC179" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -22715,32 +22723,36 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N180" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -22748,7 +22760,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22772,17 +22784,17 @@
       </c>
       <c r="X180" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y180" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z180" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA180" s="2" t="inlineStr">
@@ -22792,17 +22804,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -22922,7 +22934,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22972,7 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq37，推进9站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
@@ -22988,7 +23000,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23124,7 +23136,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23178,7 +23190,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -23244,7 +23256,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23298,7 +23310,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -23364,7 +23376,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23484,7 +23496,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23604,7 +23616,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23724,7 +23736,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23778,7 +23790,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -24642,7 +24654,7 @@
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -25452,7 +25464,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25501,7 +25513,7 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25824,7 +25836,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25868,17 +25880,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26072,7 +26084,7 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q207" s="2" t="inlineStr">
@@ -26121,7 +26133,7 @@
       </c>
       <c r="AC207" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD207" s="2" t="inlineStr">
@@ -26374,7 +26386,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -27312,7 +27324,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27361,7 +27373,7 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27560,7 +27572,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27604,17 +27616,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27928,7 +27940,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27977,7 +27989,7 @@
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
@@ -28230,7 +28242,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -28424,7 +28436,7 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q226" s="2" t="inlineStr">
@@ -28473,7 +28485,7 @@
       </c>
       <c r="AC226" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD226" s="2" t="inlineStr">
@@ -28672,7 +28684,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28716,17 +28728,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28932,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28969,7 +28981,7 @@
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -29222,7 +29234,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -29292,7 +29304,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29336,12 +29348,12 @@
       </c>
       <c r="AB233" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
@@ -30284,7 +30296,7 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q241" s="2" t="inlineStr">
@@ -30328,12 +30340,12 @@
       </c>
       <c r="AB241" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC241" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD241" s="2" t="inlineStr">
@@ -30462,7 +30474,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -30780,7 +30792,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30829,7 +30841,7 @@
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
@@ -31028,7 +31040,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31072,17 +31084,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31764,7 +31776,7 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q253" s="2" t="inlineStr">
@@ -31813,7 +31825,7 @@
       </c>
       <c r="AC253" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD253" s="2" t="inlineStr">
@@ -31942,7 +31954,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -32012,7 +32024,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32056,12 +32068,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32500,7 +32512,7 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q259" s="2" t="inlineStr">
@@ -32549,7 +32561,7 @@
       </c>
       <c r="AC259" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD259" s="2" t="inlineStr">
@@ -32744,7 +32756,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32788,17 +32800,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -33488,7 +33500,7 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q267" s="2" t="inlineStr">
@@ -33537,7 +33549,7 @@
       </c>
       <c r="AC267" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD267" s="2" t="inlineStr">
@@ -33732,7 +33744,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33776,12 +33788,12 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -33910,7 +33922,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -34344,7 +34356,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34393,7 +34405,7 @@
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
@@ -34592,7 +34604,7 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q276" s="2" t="inlineStr">
@@ -34636,17 +34648,17 @@
       </c>
       <c r="AB276" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC276" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -35673,24 +35685,24 @@
       </c>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr"/>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N285" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O285" s="2" t="inlineStr">
@@ -35700,7 +35712,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35749,7 +35761,7 @@
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
@@ -35787,32 +35799,36 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr"/>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N286" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O286" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -35820,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35844,17 +35860,17 @@
       </c>
       <c r="X286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y286" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z286" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA286" s="2" t="inlineStr">
@@ -35864,12 +35880,12 @@
       </c>
       <c r="AB286" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -35917,24 +35933,24 @@
       </c>
       <c r="I287" s="2" t="inlineStr">
         <is>
-          <t>21:26</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr"/>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N287" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O287" s="2" t="inlineStr">
@@ -35944,7 +35960,7 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q287" s="2" t="inlineStr">
@@ -35993,7 +36009,7 @@
       </c>
       <c r="AC287" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD287" s="2" t="inlineStr">
@@ -36031,32 +36047,36 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr"/>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O288" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -36064,7 +36084,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36088,17 +36108,17 @@
       </c>
       <c r="X288" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y288" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z288" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA288" s="2" t="inlineStr">
@@ -36108,17 +36128,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -36184,7 +36204,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36233,7 +36253,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36304,7 +36324,7 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q290" s="2" t="inlineStr">
@@ -36348,12 +36368,12 @@
       </c>
       <c r="AB290" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC290" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD290" s="2" t="inlineStr">
